--- a/jogos_2025-03-24.xlsx
+++ b/jogos_2025-03-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -223,12 +169,12 @@
     <t>Israel Liga Leumit</t>
   </si>
   <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Italy Serie C Group C</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Northern Ireland NIFL Premiership</t>
   </si>
   <si>
@@ -250,28 +196,31 @@
     <t>Bokelj</t>
   </si>
   <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
     <t>Radnički Sr. Mitrovica</t>
   </si>
   <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
     <t>Ural</t>
   </si>
   <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Semendrija 1924</t>
+    <t>Kafr Qasim</t>
   </si>
   <si>
     <t>Hapoel Kfar Shalem</t>
   </si>
   <si>
+    <t>Hapoel Acre</t>
+  </si>
+  <si>
     <t>Mačva Šabac</t>
   </si>
   <si>
-    <t>Hapoel Acre</t>
-  </si>
-  <si>
-    <t>Kafr Qasim</t>
+    <t>Real Zaragoza</t>
   </si>
   <si>
     <t>Avellino</t>
@@ -280,9 +229,6 @@
     <t>Benevento</t>
   </si>
   <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
     <t>Dungannon Swifts</t>
   </si>
   <si>
@@ -301,28 +247,31 @@
     <t>Dečić</t>
   </si>
   <si>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
     <t>Zemun</t>
   </si>
   <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
     <t>Arsenal Tula</t>
   </si>
   <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Trajal Krusevac</t>
+    <t>Maccabi Kabilio Jaffa</t>
   </si>
   <si>
     <t>Hapoel Rishon LeZion</t>
   </si>
   <si>
+    <t>Hapoel Kfar Saba</t>
+  </si>
+  <si>
     <t>Sloboda Užice</t>
   </si>
   <si>
-    <t>Hapoel Kfar Saba</t>
-  </si>
-  <si>
-    <t>Maccabi Kabilio Jaffa</t>
+    <t>Córdoba</t>
   </si>
   <si>
     <t>Potenza Calcio</t>
@@ -331,9 +280,6 @@
     <t>Picerno</t>
   </si>
   <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
     <t>Linfield</t>
   </si>
   <si>
@@ -358,18 +304,18 @@
     <t>['5']</t>
   </si>
   <si>
+    <t>['32']</t>
+  </si>
+  <si>
     <t>['8', '62']</t>
   </si>
   <si>
+    <t>['65']</t>
+  </si>
+  <si>
     <t>['82']</t>
   </si>
   <si>
-    <t>['65']</t>
-  </si>
-  <si>
-    <t>['32']</t>
-  </si>
-  <si>
     <t>['76']</t>
   </si>
   <si>
@@ -388,13 +334,13 @@
     <t>['77']</t>
   </si>
   <si>
+    <t>['15']</t>
+  </si>
+  <si>
     <t>['58']</t>
   </si>
   <si>
     <t>['44']</t>
-  </si>
-  <si>
-    <t>['15']</t>
   </si>
   <si>
     <t>['64']</t>
@@ -770,10 +716,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD18"/>
+  <dimension ref="A1:AL18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -888,79 +834,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45740</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -975,7 +867,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L2">
         <v>2.75</v>
@@ -1050,87 +942,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AL2">
-        <v>1.29</v>
-      </c>
-      <c r="AM2">
-        <v>1.3</v>
-      </c>
-      <c r="AN2">
-        <v>1.57</v>
-      </c>
-      <c r="AO2">
-        <v>11</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>2</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>1.8</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.8</v>
-      </c>
-      <c r="BC2">
-        <v>2.63</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>104</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45740.41666666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45740</v>
       </c>
       <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1145,25 +983,25 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L3">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="M3">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="N3">
-        <v>3.93</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="P3">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q3">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
         <v>1.57</v>
@@ -1172,16 +1010,16 @@
         <v>2.25</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V3">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
         <v>1.08</v>
@@ -1190,28 +1028,28 @@
         <v>6.5</v>
       </c>
       <c r="Z3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA3">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AB3">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AC3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AD3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG3">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH3">
         <v>11</v>
@@ -1220,87 +1058,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK3" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL3">
-        <v>1.2</v>
-      </c>
-      <c r="AM3">
-        <v>1.36</v>
-      </c>
-      <c r="AN3">
-        <v>1.6</v>
-      </c>
-      <c r="AO3">
-        <v>16</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.73</v>
-      </c>
-      <c r="BC3">
-        <v>2.75</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>94</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45740.45833333334</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45740</v>
       </c>
       <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1315,162 +1099,108 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L4">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="M4">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="N4">
-        <v>5.33</v>
+        <v>3.93</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="P4">
-        <v>7.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q4">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="R4">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W4">
         <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y4">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="Z4">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AA4">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB4">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AC4">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AD4">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AG4">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH4">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AI4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ4" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK4" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL4">
-        <v>1.11</v>
-      </c>
-      <c r="AM4">
-        <v>1.28</v>
-      </c>
-      <c r="AN4">
-        <v>2.34</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.42</v>
-      </c>
-      <c r="BC4">
-        <v>3.68</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>94</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45740.45833333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45740</v>
       </c>
       <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>75</v>
-      </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1485,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L5">
         <v>2.49</v>
@@ -1560,87 +1290,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AK5" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL5">
-        <v>1.29</v>
-      </c>
-      <c r="AM5">
-        <v>1.4</v>
-      </c>
-      <c r="AN5">
-        <v>1.44</v>
-      </c>
-      <c r="AO5">
-        <v>9</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.91</v>
-      </c>
-      <c r="BC5">
-        <v>2.6</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45740.45833333334</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45740</v>
       </c>
       <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>75</v>
-      </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1655,165 +1331,111 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L6">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="M6">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="N6">
+        <v>5.33</v>
+      </c>
+      <c r="O6">
+        <v>1.42</v>
+      </c>
+      <c r="P6">
+        <v>7.8</v>
+      </c>
+      <c r="Q6">
+        <v>3.68</v>
+      </c>
+      <c r="R6">
+        <v>1.49</v>
+      </c>
+      <c r="S6">
+        <v>2.5</v>
+      </c>
+      <c r="T6">
         <v>3.2</v>
       </c>
-      <c r="O6">
-        <v>1.83</v>
-      </c>
-      <c r="P6">
-        <v>6</v>
-      </c>
-      <c r="Q6">
-        <v>2.6</v>
-      </c>
-      <c r="R6">
-        <v>1.57</v>
-      </c>
-      <c r="S6">
-        <v>2.25</v>
-      </c>
-      <c r="T6">
-        <v>3.8</v>
-      </c>
       <c r="U6">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="V6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA6">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB6">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AC6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AD6">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AG6">
         <v>1.6</v>
       </c>
       <c r="AH6">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AI6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ6" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK6" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL6">
-        <v>1.29</v>
-      </c>
-      <c r="AM6">
-        <v>1.36</v>
-      </c>
-      <c r="AN6">
-        <v>1.5</v>
-      </c>
-      <c r="AO6">
-        <v>9</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.83</v>
-      </c>
-      <c r="BC6">
-        <v>2.6</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>94</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45740.45833333334</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45740</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1822,335 +1444,227 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L7">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M7">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O7">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="P7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
       </c>
       <c r="R7">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T7">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V7">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z7">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AA7">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AD7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE7">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AF7">
+        <v>2</v>
+      </c>
+      <c r="AG7">
         <v>1.73</v>
       </c>
-      <c r="AG7">
-        <v>2</v>
-      </c>
       <c r="AH7">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AI7">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AK7" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL7">
-        <v>1.21</v>
-      </c>
-      <c r="AM7">
-        <v>1.22</v>
-      </c>
-      <c r="AN7">
-        <v>1.93</v>
-      </c>
-      <c r="AO7">
-        <v>12</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>2</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>1.8</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.53</v>
-      </c>
-      <c r="BC7">
-        <v>2.75</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>106</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45740.58333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45740</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
         <v>1</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L8">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="M8">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="N8">
+        <v>3.8</v>
+      </c>
+      <c r="O8">
+        <v>1.53</v>
+      </c>
+      <c r="P8">
+        <v>10</v>
+      </c>
+      <c r="Q8">
+        <v>2.75</v>
+      </c>
+      <c r="R8">
+        <v>1.36</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>2.63</v>
+      </c>
+      <c r="U8">
+        <v>1.44</v>
+      </c>
+      <c r="V8">
         <v>6.5</v>
       </c>
-      <c r="O8">
-        <v>1.36</v>
-      </c>
-      <c r="P8">
-        <v>7.25</v>
-      </c>
-      <c r="Q8">
-        <v>4.33</v>
-      </c>
-      <c r="R8">
-        <v>1.45</v>
-      </c>
-      <c r="S8">
-        <v>2.55</v>
-      </c>
-      <c r="T8">
-        <v>3.3</v>
-      </c>
-      <c r="U8">
+      <c r="W8">
+        <v>1.1</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>10</v>
+      </c>
+      <c r="Z8">
         <v>1.29</v>
       </c>
-      <c r="V8">
-        <v>9</v>
-      </c>
-      <c r="W8">
-        <v>1.03</v>
-      </c>
-      <c r="X8">
-        <v>1.05</v>
-      </c>
-      <c r="Y8">
-        <v>8</v>
-      </c>
-      <c r="Z8">
-        <v>1.36</v>
-      </c>
       <c r="AA8">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC8">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AD8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE8">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF8">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AH8">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AI8">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL8">
-        <v>1.08</v>
-      </c>
-      <c r="AM8">
-        <v>1.22</v>
-      </c>
-      <c r="AN8">
-        <v>2.3</v>
-      </c>
-      <c r="AO8">
-        <v>11</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.36</v>
-      </c>
-      <c r="BC8">
-        <v>4.33</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>107</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45740.58333333334</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45740</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2165,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L9">
         <v>2.2</v>
@@ -2240,156 +1754,102 @@
         <v>1.06</v>
       </c>
       <c r="AJ9" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK9" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL9">
-        <v>1.38</v>
-      </c>
-      <c r="AM9">
-        <v>1.26</v>
-      </c>
-      <c r="AN9">
-        <v>1.56</v>
-      </c>
-      <c r="AO9">
-        <v>14</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.83</v>
-      </c>
-      <c r="BC9">
-        <v>2.25</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>108</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45740.58333333334</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45740</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L10">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="M10">
-        <v>3.1</v>
+        <v>3.73</v>
       </c>
       <c r="N10">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="O10">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="Q10">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S10">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V10">
+        <v>9</v>
+      </c>
+      <c r="W10">
+        <v>1.03</v>
+      </c>
+      <c r="X10">
+        <v>1.05</v>
+      </c>
+      <c r="Y10">
         <v>8</v>
       </c>
-      <c r="W10">
-        <v>1.06</v>
-      </c>
-      <c r="X10">
-        <v>1.07</v>
-      </c>
-      <c r="Y10">
-        <v>7</v>
-      </c>
       <c r="Z10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AA10">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB10">
         <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD10">
         <v>4</v>
@@ -2398,10 +1858,10 @@
         <v>1.2</v>
       </c>
       <c r="AF10">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG10">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH10">
         <v>8</v>
@@ -2410,93 +1870,39 @@
         <v>1.05</v>
       </c>
       <c r="AJ10" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="AK10" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL10">
-        <v>1.2</v>
-      </c>
-      <c r="AM10">
-        <v>1.32</v>
-      </c>
-      <c r="AN10">
-        <v>1.74</v>
-      </c>
-      <c r="AO10">
-        <v>9</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.62</v>
-      </c>
-      <c r="BC10">
-        <v>2.75</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>94</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45740.58333333334</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45740</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2505,165 +1911,111 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L11">
-        <v>1.46</v>
+        <v>2.26</v>
       </c>
       <c r="M11">
-        <v>4.4</v>
+        <v>3.39</v>
       </c>
       <c r="N11">
-        <v>6.3</v>
+        <v>3.35</v>
       </c>
       <c r="O11">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="P11">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="Q11">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S11">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z11">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AA11">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="AB11">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AC11">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AD11">
-        <v>3.04</v>
+        <v>3.65</v>
       </c>
       <c r="AE11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH11">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AI11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL11">
-        <v>1.05</v>
-      </c>
-      <c r="AM11">
-        <v>1.19</v>
-      </c>
-      <c r="AN11">
-        <v>2.36</v>
-      </c>
-      <c r="AO11">
-        <v>7</v>
-      </c>
-      <c r="AP11">
-        <v>1.31</v>
-      </c>
-      <c r="AQ11">
-        <v>1.57</v>
-      </c>
-      <c r="AR11">
-        <v>2</v>
-      </c>
-      <c r="AS11">
-        <v>2.62</v>
-      </c>
-      <c r="AT11">
-        <v>3.58</v>
-      </c>
-      <c r="AU11">
-        <v>2.92</v>
-      </c>
-      <c r="AV11">
-        <v>2.14</v>
-      </c>
-      <c r="AW11">
-        <v>1.69</v>
-      </c>
-      <c r="AX11">
-        <v>1.38</v>
-      </c>
-      <c r="AY11">
-        <v>1.21</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.36</v>
-      </c>
-      <c r="BC11">
-        <v>3.6</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>109</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45740.6875</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45740</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" t="s">
         <v>69</v>
       </c>
-      <c r="D12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" t="s">
-        <v>87</v>
-      </c>
       <c r="F12" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2675,168 +2027,114 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L12">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="M12">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="O12">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="P12">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="Q12">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R12">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S12">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T12">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="Z12">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AA12">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="AB12">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AD12">
-        <v>3.98</v>
+        <v>3.04</v>
       </c>
       <c r="AE12">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF12">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH12">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="AI12">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL12">
-        <v>1.1</v>
-      </c>
-      <c r="AM12">
-        <v>1.23</v>
-      </c>
-      <c r="AN12">
-        <v>2.02</v>
-      </c>
-      <c r="AO12">
-        <v>13</v>
-      </c>
-      <c r="AP12">
-        <v>1.31</v>
-      </c>
-      <c r="AQ12">
-        <v>1.58</v>
-      </c>
-      <c r="AR12">
-        <v>2.01</v>
-      </c>
-      <c r="AS12">
-        <v>2.62</v>
-      </c>
-      <c r="AT12">
-        <v>3.68</v>
-      </c>
-      <c r="AU12">
-        <v>2.92</v>
-      </c>
-      <c r="AV12">
-        <v>2.12</v>
-      </c>
-      <c r="AW12">
-        <v>1.68</v>
-      </c>
-      <c r="AX12">
-        <v>1.38</v>
-      </c>
-      <c r="AY12">
-        <v>1.2</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.44</v>
-      </c>
-      <c r="BC12">
-        <v>3.4</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>94</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45740.6875</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45740</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
         <v>70</v>
       </c>
-      <c r="D13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" t="s">
-        <v>88</v>
-      </c>
       <c r="F13" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2845,162 +2143,108 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L13">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="M13">
-        <v>3.39</v>
+        <v>3.62</v>
       </c>
       <c r="N13">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="P13">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q13">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R13">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S13">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="Z13">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AA13">
-        <v>3.27</v>
+        <v>2.66</v>
       </c>
       <c r="AB13">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC13">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AD13">
-        <v>3.65</v>
+        <v>3.98</v>
       </c>
       <c r="AE13">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AG13">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AH13">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="AI13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ13" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="AK13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AL13">
-        <v>1.33</v>
-      </c>
-      <c r="AM13">
-        <v>1.25</v>
-      </c>
-      <c r="AN13">
-        <v>1.65</v>
-      </c>
-      <c r="AO13">
-        <v>9</v>
-      </c>
-      <c r="AP13">
-        <v>1.26</v>
-      </c>
-      <c r="AQ13">
-        <v>1.51</v>
-      </c>
-      <c r="AR13">
-        <v>1.9</v>
-      </c>
-      <c r="AS13">
-        <v>2.45</v>
-      </c>
-      <c r="AT13">
-        <v>3.28</v>
-      </c>
-      <c r="AU13">
-        <v>3.22</v>
-      </c>
-      <c r="AV13">
-        <v>2.32</v>
-      </c>
-      <c r="AW13">
-        <v>1.8</v>
-      </c>
-      <c r="AX13">
-        <v>1.46</v>
-      </c>
-      <c r="AY13">
-        <v>1.25</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.67</v>
-      </c>
-      <c r="BC13">
-        <v>2.4</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>94</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45740.6875</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45740</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
         <v>71</v>
       </c>
-      <c r="D14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" t="s">
-        <v>89</v>
-      </c>
       <c r="F14" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3015,7 +2259,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L14">
         <v>4.8</v>
@@ -3090,87 +2334,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK14" t="s">
-        <v>128</v>
-      </c>
-      <c r="AL14">
-        <v>2.14</v>
-      </c>
-      <c r="AM14">
-        <v>1.21</v>
-      </c>
-      <c r="AN14">
-        <v>1.14</v>
-      </c>
-      <c r="AO14">
-        <v>17</v>
-      </c>
-      <c r="AP14">
-        <v>1.19</v>
-      </c>
-      <c r="AQ14">
-        <v>1.39</v>
-      </c>
-      <c r="AR14">
-        <v>1.7</v>
-      </c>
-      <c r="AS14">
-        <v>2.12</v>
-      </c>
-      <c r="AT14">
-        <v>2.83</v>
-      </c>
-      <c r="AU14">
-        <v>3.75</v>
-      </c>
-      <c r="AV14">
-        <v>2.59</v>
-      </c>
-      <c r="AW14">
-        <v>1.98</v>
-      </c>
-      <c r="AX14">
-        <v>1.58</v>
-      </c>
-      <c r="AY14">
-        <v>1.33</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>2.79</v>
-      </c>
-      <c r="BC14">
-        <v>1.47</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>110</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45740.70833333334</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45740</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
         <v>72</v>
       </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>90</v>
-      </c>
       <c r="F15" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3185,7 +2375,7 @@
         <v>2</v>
       </c>
       <c r="K15" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L15">
         <v>8.5</v>
@@ -3260,87 +2450,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ15" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK15" t="s">
-        <v>129</v>
-      </c>
-      <c r="AL15">
-        <v>2.95</v>
-      </c>
-      <c r="AM15">
-        <v>1.12</v>
-      </c>
-      <c r="AN15">
-        <v>1.02</v>
-      </c>
-      <c r="AO15">
-        <v>10</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>1.92</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>1.88</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>3.82</v>
-      </c>
-      <c r="BC15">
-        <v>1.28</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>111</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45740.79166666666</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45740</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
         <v>73</v>
       </c>
-      <c r="D16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" t="s">
-        <v>91</v>
-      </c>
       <c r="F16" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -3355,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L16">
         <v>2.78</v>
@@ -3430,87 +2566,33 @@
         <v>1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL16">
-        <v>1.46</v>
-      </c>
-      <c r="AM16">
-        <v>1.33</v>
-      </c>
-      <c r="AN16">
-        <v>1.46</v>
-      </c>
-      <c r="AO16">
-        <v>5</v>
-      </c>
-      <c r="AP16">
-        <v>1.5</v>
-      </c>
-      <c r="AQ16">
-        <v>1.85</v>
-      </c>
-      <c r="AR16">
-        <v>2.38</v>
-      </c>
-      <c r="AS16">
-        <v>3.15</v>
-      </c>
-      <c r="AT16">
-        <v>4.3</v>
-      </c>
-      <c r="AU16">
-        <v>2.33</v>
-      </c>
-      <c r="AV16">
-        <v>1.82</v>
-      </c>
-      <c r="AW16">
-        <v>1.49</v>
-      </c>
-      <c r="AX16">
-        <v>1.29</v>
-      </c>
-      <c r="AY16">
-        <v>1.16</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>2.05</v>
-      </c>
-      <c r="BC16">
-        <v>2</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>94</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45740.8125</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45740</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
         <v>74</v>
       </c>
-      <c r="D17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" t="s">
-        <v>92</v>
-      </c>
       <c r="F17" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -3525,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L17">
         <v>2.1</v>
@@ -3600,87 +2682,33 @@
         <v>1.16</v>
       </c>
       <c r="AJ17" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK17" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL17">
-        <v>1.25</v>
-      </c>
-      <c r="AM17">
-        <v>1.18</v>
-      </c>
-      <c r="AN17">
-        <v>1.78</v>
-      </c>
-      <c r="AO17">
-        <v>9</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.67</v>
-      </c>
-      <c r="BC17">
-        <v>2.3</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>112</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45740.85416666666</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45740</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
         <v>75</v>
       </c>
-      <c r="E18" t="s">
-        <v>93</v>
-      </c>
       <c r="F18" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -3695,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L18">
         <v>1.83</v>
@@ -3770,66 +2798,12 @@
         <v>1.04</v>
       </c>
       <c r="AJ18" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL18">
-        <v>1.2</v>
-      </c>
-      <c r="AM18">
-        <v>1.22</v>
-      </c>
-      <c r="AN18">
-        <v>1.85</v>
-      </c>
-      <c r="AO18">
-        <v>9</v>
-      </c>
-      <c r="AP18">
-        <v>0</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>2</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18">
-        <v>0</v>
-      </c>
-      <c r="AV18">
-        <v>0</v>
-      </c>
-      <c r="AW18">
-        <v>1.8</v>
-      </c>
-      <c r="AX18">
-        <v>0</v>
-      </c>
-      <c r="AY18">
-        <v>0</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.57</v>
-      </c>
-      <c r="BC18">
-        <v>3.2</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>94</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45740.90625</v>
       </c>
     </row>

--- a/jogos_2025-03-24.xlsx
+++ b/jogos_2025-03-24.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="M3" t="n">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.93</v>
+        <v>5.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.88</v>
+        <v>2.16</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>6.47</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X3" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.75</v>
+        <v>3.68</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45740.45833333334</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.74</v>
+        <v>2.49</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>5.33</v>
+        <v>3.34</v>
       </c>
       <c r="O4" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.47</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.34</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.68</v>
+        <v>2.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45740.45833333334</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.93</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
         <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R5" t="n">
         <v>1.57</v>
@@ -1080,59 +1080,59 @@
         <v>2.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI5" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45740.45833333334</v>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,19 +1185,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
         <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
@@ -1209,25 +1209,25 @@
         <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA6" t="n">
         <v>5.5</v>
@@ -1236,29 +1236,29 @@
         <v>1.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
         <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ6" t="n">
         <v>2.6</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sloboda Užice</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,37 +1314,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.73</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
         <v>1.36</v>
@@ -1353,44 +1353,44 @@
         <v>2.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AA7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>4.33</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45740.58333333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Sloboda Užice</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,37 +1443,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.73</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
         <v>1.36</v>
@@ -1482,44 +1482,44 @@
         <v>2.88</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45740.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,19 +1933,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.39</v>
+        <v>3.62</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y12" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="Z12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.44</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45740.6875</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>2.26</v>
       </c>
       <c r="M13" t="n">
-        <v>3.62</v>
+        <v>3.39</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X13" t="n">
-        <v>2.66</v>
+        <v>3.27</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.98</v>
+        <v>3.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45740.6875</v>
